--- a/Testcase/UMPay Mobile Test Cases.xlsx
+++ b/Testcase/UMPay Mobile Test Cases.xlsx
@@ -14,9 +14,10 @@
     <sheet name="Transfer" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Convert" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Global_Transfer" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="End_To_End" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Test Result" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="METADATA" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Profile" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="End_To_End" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Test Result" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="METADATA" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1055,6 +1056,501 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="3" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>Test Cases (n)</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>Test Cases (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C3" s="9">
+        <f>COUNTIF(Login!K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F3" s="9">
+        <f>COUNTIF(Register!K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K3">
+        <f>SUM(C3,F3,C8,F8,C13,F13,C18,F18,C23)</f>
+        <v/>
+      </c>
+      <c r="L3" s="15">
+        <f>IFERROR(K3/$K$6,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C4" s="9">
+        <f>COUNTIF(Login!K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F4" s="9">
+        <f>COUNTIF(Register!K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K4">
+        <f>SUM(C4,F4,C9,F9,C14,F14,C19,F19,C24)</f>
+        <v/>
+      </c>
+      <c r="L4" s="15">
+        <f>IFERROR(K4/$K$6,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C5" s="9">
+        <f>COUNTIF(Login!K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F5" s="9">
+        <f>COUNTIF(Register!K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K5">
+        <f>SUM(C5,F5,C10,F10,C15,F15,C20,F20,C25)</f>
+        <v/>
+      </c>
+      <c r="L5" s="15">
+        <f>IFERROR(K5/$K$6,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="K6" s="1">
+        <f>SUM(K3,K4,K5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Withdraw</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C8" s="9">
+        <f>COUNTIF(Deposit!K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F8" s="9">
+        <f>COUNTIF(Withdraw!K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C9" s="9">
+        <f>COUNTIF(Deposit!K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F9" s="9">
+        <f>COUNTIF(Withdraw!K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K9">
+        <f>SUM(Login!P3,Register!P3,Deposit!P3,Withdraw!P3,Transfer!P3,Convert!P3,Global_Transfer!P3,Profile!P3,End_To_End!P3)</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>SUM(Login!Q3,Register!Q3,Deposit!Q3,Withdraw!Q3,Transfer!Q3,Convert!Q3,Global_Transfer!Q3,Profile!Q3,End_To_End!Q3)</f>
+        <v/>
+      </c>
+      <c r="M9">
+        <f>SUM(Login!R3,Register!R3,Deposit!R3,Withdraw!R3,Transfer!R3,Convert!R3,Global_Transfer!R3,Profile!R3,End_To_End!R3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C10" s="9">
+        <f>COUNTIF(Deposit!K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F10" s="9">
+        <f>COUNTIF(Withdraw!K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K10">
+        <f>SUM(Login!P4,Register!P4,Deposit!P4,Withdraw!P4,Transfer!P4,Convert!P4,Global_Transfer!P4,Profile!P4,End_To_End!P4)</f>
+        <v/>
+      </c>
+      <c r="L10">
+        <f>SUM(Login!Q4,Register!Q4,Deposit!Q4,Withdraw!Q4,Transfer!Q4,Convert!Q4,Global_Transfer!Q4,Profile!Q4,End_To_End!Q4)</f>
+        <v/>
+      </c>
+      <c r="M10">
+        <f>SUM(Login!R4,Register!R4,Deposit!R4,Withdraw!R4,Transfer!R4,Convert!R4,Global_Transfer!R4,Profile!R4,End_To_End!R4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K11">
+        <f>SUM(Login!P5,Register!P5,Deposit!P5,Withdraw!P5,Transfer!P5,Convert!P5,Global_Transfer!P5,Profile!P5,End_To_End!P5)</f>
+        <v/>
+      </c>
+      <c r="L11">
+        <f>SUM(Login!Q5,Register!Q5,Deposit!Q5,Withdraw!Q5,Transfer!Q5,Convert!Q5,Global_Transfer!Q5,Profile!Q5,End_To_End!Q5)</f>
+        <v/>
+      </c>
+      <c r="M11">
+        <f>SUM(Login!R5,Register!R5,Deposit!R5,Withdraw!R5,Transfer!R5,Convert!R5,Global_Transfer!R5,Profile!R5,End_To_End!R5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Convert</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C13" s="9">
+        <f>COUNTIF(Transfer!K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F13" s="9">
+        <f>COUNTIF(Convert!K:K,"PASS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C14" s="9">
+        <f>COUNTIF(Transfer!K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F14" s="9">
+        <f>COUNTIF(Convert!K:K,"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C15" s="9">
+        <f>COUNTIF(Transfer!K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F15" s="9">
+        <f>COUNTIF(Convert!K:K,"PENDING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Global_Transfer</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C18" s="9">
+        <f>COUNTIF(Global_Transfer!K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F18" s="9">
+        <f>COUNTIF(Profile!K:K,"PASS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C19" s="9">
+        <f>COUNTIF(Global_Transfer!K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F19" s="9">
+        <f>COUNTIF(Profile!K:K,"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C20" s="9">
+        <f>COUNTIF(Global_Transfer!K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F20" s="9">
+        <f>COUNTIF(Profile!K:K,"PENDING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>End_To_End</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C23" s="9">
+        <f>COUNTIF(End_To_End!K:K,"PASS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C24" s="9">
+        <f>COUNTIF(End_To_End!K:K,"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C25" s="9">
+        <f>COUNTIF(End_To_End!K:K,"PENDING")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4392,6 +4888,570 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12.6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UMPay Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Profile.feature</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>46274</v>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>The profile panel offers everything the account holder can reach</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-Then the profile panel should offer "Trade Record, User List, Commission Listing, Fee Listing, Wallets, Payment, Templates, Transfer Fee Setting, Security, Document verification, Language"</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>The profile panel should offer "Trade Record, User List, Commission Listing, Fee Listing, Wallets, Payment, Templates, Transfer Fee Setting, Security, Document verification, Language"</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>The profile panel shows the account's referral code</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-Then the profile panel should show a referral code</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>The profile panel should show a referral code</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TC_003</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Each destination in the profile panel opens its own screen</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "&lt;destination&gt;" from the profile panel
+-Then the "&lt;destination&gt;" screen should open
+-When I go back from the destination
+-Then the profile panel should offer "&lt;destination&gt;"</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>The "&lt;destination&gt;" screen should open; the profile panel should offer "&lt;destination&gt;"</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="n"/>
+      <c r="R11" s="4" t="n"/>
+      <c r="S11" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="K9:K11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9:L11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Positive,Negative"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4794,459 +5854,4 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:M20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="3" customWidth="1" min="7" max="7"/>
-    <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="3" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Login</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>Register</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="K2" s="7" t="inlineStr">
-        <is>
-          <t>Test Cases (n)</t>
-        </is>
-      </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t>Test Cases (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C3" s="9">
-        <f>COUNTIF(Login!K:K,"PASS")</f>
-        <v/>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F3" s="9">
-        <f>COUNTIF(Register!K:K,"PASS")</f>
-        <v/>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K3">
-        <f>SUM(C3,F3,C8,F8,C13,F13,C18,F18)</f>
-        <v/>
-      </c>
-      <c r="L3" s="15">
-        <f>IFERROR(K3/$K$6,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="C4" s="9">
-        <f>COUNTIF(Login!K:K,"FAIL")</f>
-        <v/>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F4" s="9">
-        <f>COUNTIF(Register!K:K,"FAIL")</f>
-        <v/>
-      </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K4">
-        <f>SUM(C4,F4,C9,F9,C14,F14,C19,F19)</f>
-        <v/>
-      </c>
-      <c r="L4" s="15">
-        <f>IFERROR(K4/$K$6,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="C5" s="9">
-        <f>COUNTIF(Login!K:K,"PENDING")</f>
-        <v/>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="F5" s="9">
-        <f>COUNTIF(Register!K:K,"PENDING")</f>
-        <v/>
-      </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K5">
-        <f>SUM(C5,F5,C10,F10,C15,F15,C20,F20)</f>
-        <v/>
-      </c>
-      <c r="L5" s="15">
-        <f>IFERROR(K5/$K$6,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="K6" s="1">
-        <f>SUM(K3,K4,K5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Withdraw</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C8" s="9">
-        <f>COUNTIF(Deposit!K:K,"PASS")</f>
-        <v/>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F8" s="9">
-        <f>COUNTIF(Withdraw!K:K,"PASS")</f>
-        <v/>
-      </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M8" s="1" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="C9" s="9">
-        <f>COUNTIF(Deposit!K:K,"FAIL")</f>
-        <v/>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F9" s="9">
-        <f>COUNTIF(Withdraw!K:K,"FAIL")</f>
-        <v/>
-      </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K9">
-        <f>SUM(Login!P3,Register!P3,Deposit!P3,Withdraw!P3,Transfer!P3,Convert!P3,Global_Transfer!P3,End_To_End!P3)</f>
-        <v/>
-      </c>
-      <c r="L9">
-        <f>SUM(Login!Q3,Register!Q3,Deposit!Q3,Withdraw!Q3,Transfer!Q3,Convert!Q3,Global_Transfer!Q3,End_To_End!Q3)</f>
-        <v/>
-      </c>
-      <c r="M9">
-        <f>SUM(Login!R3,Register!R3,Deposit!R3,Withdraw!R3,Transfer!R3,Convert!R3,Global_Transfer!R3,End_To_End!R3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="C10" s="9">
-        <f>COUNTIF(Deposit!K:K,"PENDING")</f>
-        <v/>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="F10" s="9">
-        <f>COUNTIF(Withdraw!K:K,"PENDING")</f>
-        <v/>
-      </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K10">
-        <f>SUM(Login!P4,Register!P4,Deposit!P4,Withdraw!P4,Transfer!P4,Convert!P4,Global_Transfer!P4,End_To_End!P4)</f>
-        <v/>
-      </c>
-      <c r="L10">
-        <f>SUM(Login!Q4,Register!Q4,Deposit!Q4,Withdraw!Q4,Transfer!Q4,Convert!Q4,Global_Transfer!Q4,End_To_End!Q4)</f>
-        <v/>
-      </c>
-      <c r="M10">
-        <f>SUM(Login!R4,Register!R4,Deposit!R4,Withdraw!R4,Transfer!R4,Convert!R4,Global_Transfer!R4,End_To_End!R4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K11">
-        <f>SUM(Login!P5,Register!P5,Deposit!P5,Withdraw!P5,Transfer!P5,Convert!P5,Global_Transfer!P5,End_To_End!P5)</f>
-        <v/>
-      </c>
-      <c r="L11">
-        <f>SUM(Login!Q5,Register!Q5,Deposit!Q5,Withdraw!Q5,Transfer!Q5,Convert!Q5,Global_Transfer!Q5,End_To_End!Q5)</f>
-        <v/>
-      </c>
-      <c r="M11">
-        <f>SUM(Login!R5,Register!R5,Deposit!R5,Withdraw!R5,Transfer!R5,Convert!R5,Global_Transfer!R5,End_To_End!R5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Transfer</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Convert</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C13" s="9">
-        <f>COUNTIF(Transfer!K:K,"PASS")</f>
-        <v/>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F13" s="9">
-        <f>COUNTIF(Convert!K:K,"PASS")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="C14" s="9">
-        <f>COUNTIF(Transfer!K:K,"FAIL")</f>
-        <v/>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F14" s="9">
-        <f>COUNTIF(Convert!K:K,"FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="C15" s="9">
-        <f>COUNTIF(Transfer!K:K,"PENDING")</f>
-        <v/>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="F15" s="9">
-        <f>COUNTIF(Convert!K:K,"PENDING")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Global_Transfer</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>End_To_End</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C18" s="9">
-        <f>COUNTIF(Global_Transfer!K:K,"PASS")</f>
-        <v/>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F18" s="9">
-        <f>COUNTIF(End_To_End!K:K,"PASS")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="C19" s="9">
-        <f>COUNTIF(Global_Transfer!K:K,"FAIL")</f>
-        <v/>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F19" s="9">
-        <f>COUNTIF(End_To_End!K:K,"FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="C20" s="9">
-        <f>COUNTIF(Global_Transfer!K:K,"PENDING")</f>
-        <v/>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="F20" s="9">
-        <f>COUNTIF(End_To_End!K:K,"PENDING")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Testcase/UMPay Mobile Test Cases.xlsx
+++ b/Testcase/UMPay Mobile Test Cases.xlsx
@@ -15,9 +15,10 @@
     <sheet name="Convert" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Global_Transfer" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Profile" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="End_To_End" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Test Result" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="METADATA" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Wallets" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="End_To_End" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Test Result" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="METADATA" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,6 +1057,416 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:S9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12.6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UMPay Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>End To End</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EndToEndTest.feature</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>46274</v>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>End To End</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>A user signs in, fills every money form, prices a transfer and signs out</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>The UMPay app is open on the login screen</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>-Given the UMPay app is open on the login screen
+-When I sign in with the credentials in "1" of "Sheet1" of "Login_TestData.xlsx"
+-Then I should reach the dashboard
+-And the dashboard should offer the money actions
+-When I open the "Deposit" form from the dashboard
+-Then the "Deposit" form should be shown
+-And the "Confirm" action should be disabled
+-When I enter the deposit amount in "1" of "Sheet1" of "Deposit_TestData.xlsx"
+-Then the amount should be accepted
+-And the form should ask for "Payment information"
+-And the transaction is deliberately not submitted
+-When I open the "Withdrawal" form from the dashboard
+-Then the "Withdrawal" form should be shown
+-When I enter the withdrawal amount in "1" of "Sheet1" of "Withdraw_TestData.xlsx"
+-Then the amount should be accepted
+-And the transaction is deliberately not submitted
+-When I open the "Convert" form from the dashboard
+-Then the "Convert" form should be shown
+-When I enter the conversion amount in "1" of "Sheet1" of "Convert_TestData.xlsx"
+-Then the amount should be accepted
+-And the transaction is deliberately not submitted
+-When I open the transfer hub
+-Then the transfer hub should offer the route "UMPay to Existing template"
+-And the transfer hub should offer the route "UMPay to UMPay Wallet"
+-When I take the "UnionPay China" route
+-Then the UnionPay transfer form should be shown
+-When I enter the UnionPay amount in "1" of "Sheet1" of "GlobalTransfer_TestData.xlsx"
+-Then the transfer should be priced
+-And the UnionPay transfer should become sendable
+-And the transfer is deliberately not sent
+-When I sign out
+-Then I should be back on the login screen</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Convert_TestData.xlsx, Deposit_TestData.xlsx, GlobalTransfer_TestData.xlsx, Login_TestData.xlsx, Withdraw_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>I should reach the dashboard; the dashboard should offer the money actions; the "Deposit" form should be shown; the "Confirm" action should be disabled; the amount should be accepted; the form should ask for "Payment information"; the transaction is deliberately not submitted; the "Withdrawal" form should be shown</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Not run in this pass. The runner holds @register and @e2e back from an unattended run - a registration makes a real account, solves a captcha and reads a code out of a mailbox, and the journey drives every form a second time on the one device this suite has. Launch it on its own with the Run link beside this row</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="K9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Positive,Negative"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B2:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1126,7 +1537,7 @@
         </is>
       </c>
       <c r="K3">
-        <f>SUM(C3,F3,C8,F8,C13,F13,C18,F18,C23)</f>
+        <f>SUM(C3,F3,C8,F8,C13,F13,C18,F18,C23,F23)</f>
         <v/>
       </c>
       <c r="L3" s="15">
@@ -1159,7 +1570,7 @@
         </is>
       </c>
       <c r="K4">
-        <f>SUM(C4,F4,C9,F9,C14,F14,C19,F19,C24)</f>
+        <f>SUM(C4,F4,C9,F9,C14,F14,C19,F19,C24,F24)</f>
         <v/>
       </c>
       <c r="L4" s="15">
@@ -1192,7 +1603,7 @@
         </is>
       </c>
       <c r="K5">
-        <f>SUM(C5,F5,C10,F10,C15,F15,C20,F20,C25)</f>
+        <f>SUM(C5,F5,C10,F10,C15,F15,C20,F20,C25,F25)</f>
         <v/>
       </c>
       <c r="L5" s="15">
@@ -1288,15 +1699,15 @@
         </is>
       </c>
       <c r="K9">
-        <f>SUM(Login!P3,Register!P3,Deposit!P3,Withdraw!P3,Transfer!P3,Convert!P3,Global_Transfer!P3,Profile!P3,End_To_End!P3)</f>
+        <f>SUM(Login!P3,Register!P3,Deposit!P3,Withdraw!P3,Transfer!P3,Convert!P3,Global_Transfer!P3,Profile!P3,Wallets!P3,End_To_End!P3)</f>
         <v/>
       </c>
       <c r="L9">
-        <f>SUM(Login!Q3,Register!Q3,Deposit!Q3,Withdraw!Q3,Transfer!Q3,Convert!Q3,Global_Transfer!Q3,Profile!Q3,End_To_End!Q3)</f>
+        <f>SUM(Login!Q3,Register!Q3,Deposit!Q3,Withdraw!Q3,Transfer!Q3,Convert!Q3,Global_Transfer!Q3,Profile!Q3,Wallets!Q3,End_To_End!Q3)</f>
         <v/>
       </c>
       <c r="M9">
-        <f>SUM(Login!R3,Register!R3,Deposit!R3,Withdraw!R3,Transfer!R3,Convert!R3,Global_Transfer!R3,Profile!R3,End_To_End!R3)</f>
+        <f>SUM(Login!R3,Register!R3,Deposit!R3,Withdraw!R3,Transfer!R3,Convert!R3,Global_Transfer!R3,Profile!R3,Wallets!R3,End_To_End!R3)</f>
         <v/>
       </c>
     </row>
@@ -1325,15 +1736,15 @@
         </is>
       </c>
       <c r="K10">
-        <f>SUM(Login!P4,Register!P4,Deposit!P4,Withdraw!P4,Transfer!P4,Convert!P4,Global_Transfer!P4,Profile!P4,End_To_End!P4)</f>
+        <f>SUM(Login!P4,Register!P4,Deposit!P4,Withdraw!P4,Transfer!P4,Convert!P4,Global_Transfer!P4,Profile!P4,Wallets!P4,End_To_End!P4)</f>
         <v/>
       </c>
       <c r="L10">
-        <f>SUM(Login!Q4,Register!Q4,Deposit!Q4,Withdraw!Q4,Transfer!Q4,Convert!Q4,Global_Transfer!Q4,Profile!Q4,End_To_End!Q4)</f>
+        <f>SUM(Login!Q4,Register!Q4,Deposit!Q4,Withdraw!Q4,Transfer!Q4,Convert!Q4,Global_Transfer!Q4,Profile!Q4,Wallets!Q4,End_To_End!Q4)</f>
         <v/>
       </c>
       <c r="M10">
-        <f>SUM(Login!R4,Register!R4,Deposit!R4,Withdraw!R4,Transfer!R4,Convert!R4,Global_Transfer!R4,Profile!R4,End_To_End!R4)</f>
+        <f>SUM(Login!R4,Register!R4,Deposit!R4,Withdraw!R4,Transfer!R4,Convert!R4,Global_Transfer!R4,Profile!R4,Wallets!R4,End_To_End!R4)</f>
         <v/>
       </c>
     </row>
@@ -1344,15 +1755,15 @@
         </is>
       </c>
       <c r="K11">
-        <f>SUM(Login!P5,Register!P5,Deposit!P5,Withdraw!P5,Transfer!P5,Convert!P5,Global_Transfer!P5,Profile!P5,End_To_End!P5)</f>
+        <f>SUM(Login!P5,Register!P5,Deposit!P5,Withdraw!P5,Transfer!P5,Convert!P5,Global_Transfer!P5,Profile!P5,Wallets!P5,End_To_End!P5)</f>
         <v/>
       </c>
       <c r="L11">
-        <f>SUM(Login!Q5,Register!Q5,Deposit!Q5,Withdraw!Q5,Transfer!Q5,Convert!Q5,Global_Transfer!Q5,Profile!Q5,End_To_End!Q5)</f>
+        <f>SUM(Login!Q5,Register!Q5,Deposit!Q5,Withdraw!Q5,Transfer!Q5,Convert!Q5,Global_Transfer!Q5,Profile!Q5,Wallets!Q5,End_To_End!Q5)</f>
         <v/>
       </c>
       <c r="M11">
-        <f>SUM(Login!R5,Register!R5,Deposit!R5,Withdraw!R5,Transfer!R5,Convert!R5,Global_Transfer!R5,Profile!R5,End_To_End!R5)</f>
+        <f>SUM(Login!R5,Register!R5,Deposit!R5,Withdraw!R5,Transfer!R5,Convert!R5,Global_Transfer!R5,Profile!R5,Wallets!R5,End_To_End!R5)</f>
         <v/>
       </c>
     </row>
@@ -1503,6 +1914,11 @@
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
+          <t>Wallets</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
           <t>End_To_End</t>
         </is>
       </c>
@@ -1514,6 +1930,15 @@
         </is>
       </c>
       <c r="C23" s="9">
+        <f>COUNTIF(Wallets!K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F23" s="9">
         <f>COUNTIF(End_To_End!K:K,"PASS")</f>
         <v/>
       </c>
@@ -1525,6 +1950,15 @@
         </is>
       </c>
       <c r="C24" s="9">
+        <f>COUNTIF(Wallets!K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F24" s="9">
         <f>COUNTIF(End_To_End!K:K,"FAIL")</f>
         <v/>
       </c>
@@ -1536,6 +1970,15 @@
         </is>
       </c>
       <c r="C25" s="9">
+        <f>COUNTIF(Wallets!K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F25" s="9">
         <f>COUNTIF(End_To_End!K:K,"PENDING")</f>
         <v/>
       </c>
@@ -1545,7 +1988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5452,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.6" customWidth="1" min="1" max="1"/>
@@ -5496,7 +5939,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>End To End</t>
+          <t>Wallets</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -5523,7 +5966,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EndToEndTest.feature</t>
+          <t>Wallets.feature</t>
         </is>
       </c>
       <c r="N3" s="1" t="inlineStr">
@@ -5727,12 +6170,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>End To End</t>
+          <t>Wallets</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>A user signs in, fills every money form, prices a transfer and signs out</t>
+          <t>Every wallet names its currency and what it holds</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -5742,53 +6185,26 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>The UMPay app is open on the login screen</t>
+          <t>I log into the UMPay application with valid credentials</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>-Given the UMPay app is open on the login screen
--When I sign in with the credentials in "1" of "Sheet1" of "Login_TestData.xlsx"
--Then I should reach the dashboard
--And the dashboard should offer the money actions
--When I open the "Deposit" form from the dashboard
--Then the "Deposit" form should be shown
--And the "Confirm" action should be disabled
--When I enter the deposit amount in "1" of "Sheet1" of "Deposit_TestData.xlsx"
--Then the amount should be accepted
--And the form should ask for "Payment information"
--And the transaction is deliberately not submitted
--When I open the "Withdrawal" form from the dashboard
--Then the "Withdrawal" form should be shown
--When I enter the withdrawal amount in "1" of "Sheet1" of "Withdraw_TestData.xlsx"
--Then the amount should be accepted
--And the transaction is deliberately not submitted
--When I open the "Convert" form from the dashboard
--Then the "Convert" form should be shown
--When I enter the conversion amount in "1" of "Sheet1" of "Convert_TestData.xlsx"
--Then the amount should be accepted
--And the transaction is deliberately not submitted
--When I open the transfer hub
--Then the transfer hub should offer the route "UMPay to Existing template"
--And the transfer hub should offer the route "UMPay to UMPay Wallet"
--When I take the "UnionPay China" route
--Then the UnionPay transfer form should be shown
--When I enter the UnionPay amount in "1" of "Sheet1" of "GlobalTransfer_TestData.xlsx"
--Then the transfer should be priced
--And the UnionPay transfer should become sendable
--And the transfer is deliberately not sent
--When I sign out
--Then I should be back on the login screen</t>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Wallets" from the profile panel
+-Then the "Wallets" screen should open
+-And every wallet should name its currency and what it holds</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Convert_TestData.xlsx, Deposit_TestData.xlsx, GlobalTransfer_TestData.xlsx, Login_TestData.xlsx, Withdraw_TestData.xlsx</t>
+          <t>Login_TestData.xlsx</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>I should reach the dashboard; the dashboard should offer the money actions; the "Deposit" form should be shown; the "Confirm" action should be disabled; the amount should be accepted; the form should ask for "Payment information"; the transaction is deliberately not submitted; the "Withdrawal" form should be shown</t>
+          <t>The "Wallets" screen should open; every wallet should name its currency and what it holds</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -5798,17 +6214,17 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Not run in this pass. The runner holds @register and @e2e back from an unattended run - a registration makes a real account, solves a captcha and reads a code out of a mailbox, and the journey drives every form a second time on the one device this suite has. Launch it on its own with the Run link beside this row</t>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -5837,20 +6253,756 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Wallets</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Exactly one wallet is the main wallet</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Wallets" from the profile panel
+-Then the "Wallets" screen should open
+-And exactly one wallet should be the main wallet</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>The "Wallets" screen should open; exactly one wallet should be the main wallet</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TC_003</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Wallets</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>What is held against the account is written as a deduction</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Wallets" from the profile panel
+-Then the "Wallets" screen should open
+-And what is held against the account should be written as a deduction</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>The "Wallets" screen should open; what is held against the account should be written as a deduction</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="n"/>
+      <c r="R11" s="4" t="n"/>
+      <c r="S11" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TC_004</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Wallets</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Every user is listed with a number, a name and a status</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "User List" from the profile panel
+-Then the "User List" screen should open
+-And every user should be listed with a number, a name and a status</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>The "User List" screen should open; every user should be listed with a number, a name and a status</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="n"/>
+      <c r="R12" s="4" t="n"/>
+      <c r="S12" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>TC_005</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Wallets</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Every user is listed under a proper account number</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "User List" from the profile panel
+-Then the "User List" screen should open
+-And every account number should read as one the platform issues</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>The "User List" screen should open; every account number should read as one the platform issues</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="n"/>
+      <c r="R13" s="4" t="n"/>
+      <c r="S13" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>TC_006</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Wallets</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Nobody is listed twice</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "User List" from the profile panel
+-Then the "User List" screen should open
+-And nobody should be listed twice</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>The "User List" screen should open; nobody should be listed twice</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="n"/>
+      <c r="R14" s="4" t="n"/>
+      <c r="S14" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>TC_007</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Wallets</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Every status is one the platform uses</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "User List" from the profile panel
+-Then the "User List" screen should open
+-And every status should be one of "Unlock, Lock, Locked"</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>The "User List" screen should open; every status should be one of "Unlock, Lock, Locked"</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="n"/>
+      <c r="R15" s="4" t="n"/>
+      <c r="S15" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>TC_008</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Wallets</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Every currency the platform deals in can be asked about</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Fee Listing" from the profile panel
+-Then the "Fee Listing" screen should open
+-And the fee listing should offer "BDT, BRL, HKD, IDR, MXN, MYR, PHP"</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>The "Fee Listing" screen should open; the fee listing should offer "BDT, BRL, HKD, IDR, MXN, MYR, PHP"</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="n"/>
+      <c r="R16" s="4" t="n"/>
+      <c r="S16" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>TC_009</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Wallets</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Each currency is offered exactly once</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Fee Listing" from the profile panel
+-Then the "Fee Listing" screen should open
+-And each currency should be offered exactly once</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>The "Fee Listing" screen should open; each currency should be offered exactly once</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="n"/>
+      <c r="R17" s="4" t="n"/>
+      <c r="S17" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="K9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K9:K17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PASS,FAIL,PENDING"</formula1>
     </dataValidation>
-    <dataValidation sqref="L9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L9:L17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
     </dataValidation>
-    <dataValidation sqref="D9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D9:D17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Positive,Negative"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Testcase/UMPay Mobile Test Cases.xlsx
+++ b/Testcase/UMPay Mobile Test Cases.xlsx
@@ -16,9 +16,17 @@
     <sheet name="Global_Transfer" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Profile" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Wallets" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="End_To_End" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Test Result" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="METADATA" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Home" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Bills" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Trade_Record" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Commission_Listing" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Payment" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Template" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Transfer_Fee_Setting" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Security" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="End_To_End" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Test Result" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="METADATA" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -567,7 +575,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UMPayLogin.feature</t>
+          <t>Login.feature</t>
         </is>
       </c>
       <c r="N3" s="1" t="inlineStr">
@@ -632,7 +640,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -663,7 +671,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="8">
@@ -831,7 +839,7 @@
         </is>
       </c>
       <c r="N9" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -921,7 +929,7 @@
         </is>
       </c>
       <c r="N10" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
@@ -1010,7 +1018,7 @@
         </is>
       </c>
       <c r="N11" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -1052,6 +1060,3889 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12.6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UMPay Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Home.feature</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>46275</v>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>The dashboard offers every flow the account can start</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-Then the dashboard should offer "Deposit, Withdrawal, Transfer, Convert, Bills, International School Fee"</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>The dashboard should offer "Deposit, Withdrawal, Transfer, Convert, Bills, International School Fee"</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>The amounts on the dashboard arrive hidden</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-Then the amounts on the dashboard should be hidden</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>The amounts on the dashboard should be hidden</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="K9:K10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9:L10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Positive,Negative"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12.6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UMPay Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bills.feature</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>46275</v>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>The bills list what the account has done</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open Bills from the dashboard
+-Then the "Bills" screen should open
+-And the screen should list something</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>The "Bills" screen should open; the screen should list something</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Every transaction names its kind, its date and its amount</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open Bills from the dashboard
+-Then the "Bills" screen should open
+-And every bill should name its kind, its date and its amount</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>The "Bills" screen should open; every bill should name its kind, its date and its amount</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TC_003</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>The ledger offers to be narrowed</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open Bills from the dashboard
+-Then the "Bills" screen should open
+-And the screen should carry "Filter"</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>The "Bills" screen should open; the screen should carry "Filter"</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="n"/>
+      <c r="R11" s="4" t="n"/>
+      <c r="S11" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="K9:K11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9:L11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Positive,Negative"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12.6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UMPay Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Trade Record</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TradeRecord.feature</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>46275</v>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Trade Record</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>The trade record lists the orders the account has raised</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Trade Record" from the profile panel
+-Then the "Trade Record" screen should open
+-And the screen should list something</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>The "Trade Record" screen should open; the screen should list something</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Trade Record</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>The trade record is kept in its own tabs</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Trade Record" from the profile panel
+-Then the "Trade Record" screen should open
+-And the screen should carry "Deposit/Withdrawal, International Transfer"</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>The "Trade Record" screen should open; the screen should carry "Deposit/Withdrawal, International Transfer"</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="K9:K10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9:L10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Positive,Negative"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12.6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UMPay Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Commission Listing</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CommissionListing.feature</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>46275</v>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Commission Listing</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>The commission listing shows what the account has earned</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Commission Listing" from the profile panel
+-Then the "Commission Listing" screen should open
+-And the screen should list something</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>The "Commission Listing" screen should open; the screen should list something</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Commission Listing</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>The commissions can be narrowed</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Commission Listing" from the profile panel
+-Then the "Commission Listing" screen should open
+-And the screen should carry "Filter"</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>The "Commission Listing" screen should open; the screen should carry "Filter"</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="K9:K10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9:L10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Positive,Negative"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12.6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UMPay Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Payment.feature</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>46275</v>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>The saved payment accounts are listed</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Payment" from the profile panel
+-Then the "Payment" screen should open
+-And the screen should list something</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>The "Payment" screen should open; the screen should list something</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Every saved account names what identifies it</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Payment" from the profile panel
+-Then the "Payment" screen should open
+-And the screen should carry "Account Name, Account Number"</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>The "Payment" screen should open; the screen should carry "Account Name, Account Number"</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="K9:K10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9:L10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Positive,Negative"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12.6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UMPay Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Template.feature</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>46275</v>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>The saved templates are listed</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Templates" from the profile panel
+-Then the "Templates" screen should open
+-And the screen should list something</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>The "Templates" screen should open; the screen should list something</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>The page offers to add a template</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Templates" from the profile panel
+-Then the "Templates" screen should open
+-And the screen should carry "Add Template"</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>The "Templates" screen should open; the screen should carry "Add Template"</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="K9:K10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9:L10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Positive,Negative"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12.6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UMPay Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Transfer Fee Setting</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TransferFeeSetting.feature</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>46275</v>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Transfer Fee Setting</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>The page offers every way the fee can be settled</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Transfer Fee Setting" from the profile panel
+-Then the "Transfer Fee Setting" screen should open
+-And the screen should carry "Fee will be selected by user, Fee will always be paid by other party, Fee will always be paid by me"</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>The "Transfer Fee Setting" screen should open; the screen should carry "Fee will be selected by user, Fee will always be paid by other party, Fee will always be paid by me"</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Transfer Fee Setting</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>The page says what it is asking and offers to save it</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Transfer Fee Setting" from the profile panel
+-Then the "Transfer Fee Setting" screen should open
+-And the screen should carry "Select who will pay the fee, Update"</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>The "Transfer Fee Setting" screen should open; the screen should carry "Select who will pay the fee, Update"</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="K9:K10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9:L10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Positive,Negative"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12.6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UMPay Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Security.feature</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>46275</v>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>The page offers everything the account is guarded by</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Security" from the profile panel
+-Then the "Security" screen should open
+-And the screen should carry "Login Password, PIN, 2FA Authenticator"</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>The "Security" screen should open; the screen should carry "Login Password, PIN, 2FA Authenticator"</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>The phone offers a biometric sign in the web has no equivalent for</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>I log into the UMPay application with valid credentials</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid credentials using "1" of "Sheet1" of "Login_TestData.xlsx"
+-When I open the profile panel
+-And I open "Security" from the profile panel
+-Then the "Security" screen should open
+-And the screen should carry "Biometric Login"</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Login_TestData.xlsx</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>The "Security" screen should open; the screen should carry "Biometric Login"</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>The app is left on the screen the scenario reached</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="14" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="K9:K10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9:L10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Positive,Negative"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1193,7 +5084,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -1224,7 +5115,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="8">
@@ -1422,7 +5313,7 @@
         </is>
       </c>
       <c r="N9" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -1461,13 +5352,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M25"/>
+  <dimension ref="B2:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1537,7 +5428,7 @@
         </is>
       </c>
       <c r="K3">
-        <f>SUM(C3,F3,C8,F8,C13,F13,C18,F18,C23,F23)</f>
+        <f>SUM(C3,F3,C8,F8,C13,F13,C18,F18,C23,F23,C28,F28,C33,F33,C38,F38,C43,F43)</f>
         <v/>
       </c>
       <c r="L3" s="15">
@@ -1570,7 +5461,7 @@
         </is>
       </c>
       <c r="K4">
-        <f>SUM(C4,F4,C9,F9,C14,F14,C19,F19,C24,F24)</f>
+        <f>SUM(C4,F4,C9,F9,C14,F14,C19,F19,C24,F24,C29,F29,C34,F34,C39,F39,C44,F44)</f>
         <v/>
       </c>
       <c r="L4" s="15">
@@ -1603,7 +5494,7 @@
         </is>
       </c>
       <c r="K5">
-        <f>SUM(C5,F5,C10,F10,C15,F15,C20,F20,C25,F25)</f>
+        <f>SUM(C5,F5,C10,F10,C15,F15,C20,F20,C25,F25,C30,F30,C35,F35,C40,F40,C45,F45)</f>
         <v/>
       </c>
       <c r="L5" s="15">
@@ -1699,15 +5590,15 @@
         </is>
       </c>
       <c r="K9">
-        <f>SUM(Login!P3,Register!P3,Deposit!P3,Withdraw!P3,Transfer!P3,Convert!P3,Global_Transfer!P3,Profile!P3,Wallets!P3,End_To_End!P3)</f>
+        <f>SUM(Login!P3,Register!P3,Deposit!P3,Withdraw!P3,Transfer!P3,Convert!P3,Global_Transfer!P3,Profile!P3,Wallets!P3,Home!P3,Bills!P3,Trade_Record!P3,Commission_Listing!P3,Payment!P3,Template!P3,Transfer_Fee_Setting!P3,Security!P3,End_To_End!P3)</f>
         <v/>
       </c>
       <c r="L9">
-        <f>SUM(Login!Q3,Register!Q3,Deposit!Q3,Withdraw!Q3,Transfer!Q3,Convert!Q3,Global_Transfer!Q3,Profile!Q3,Wallets!Q3,End_To_End!Q3)</f>
+        <f>SUM(Login!Q3,Register!Q3,Deposit!Q3,Withdraw!Q3,Transfer!Q3,Convert!Q3,Global_Transfer!Q3,Profile!Q3,Wallets!Q3,Home!Q3,Bills!Q3,Trade_Record!Q3,Commission_Listing!Q3,Payment!Q3,Template!Q3,Transfer_Fee_Setting!Q3,Security!Q3,End_To_End!Q3)</f>
         <v/>
       </c>
       <c r="M9">
-        <f>SUM(Login!R3,Register!R3,Deposit!R3,Withdraw!R3,Transfer!R3,Convert!R3,Global_Transfer!R3,Profile!R3,Wallets!R3,End_To_End!R3)</f>
+        <f>SUM(Login!R3,Register!R3,Deposit!R3,Withdraw!R3,Transfer!R3,Convert!R3,Global_Transfer!R3,Profile!R3,Wallets!R3,Home!R3,Bills!R3,Trade_Record!R3,Commission_Listing!R3,Payment!R3,Template!R3,Transfer_Fee_Setting!R3,Security!R3,End_To_End!R3)</f>
         <v/>
       </c>
     </row>
@@ -1736,15 +5627,15 @@
         </is>
       </c>
       <c r="K10">
-        <f>SUM(Login!P4,Register!P4,Deposit!P4,Withdraw!P4,Transfer!P4,Convert!P4,Global_Transfer!P4,Profile!P4,Wallets!P4,End_To_End!P4)</f>
+        <f>SUM(Login!P4,Register!P4,Deposit!P4,Withdraw!P4,Transfer!P4,Convert!P4,Global_Transfer!P4,Profile!P4,Wallets!P4,Home!P4,Bills!P4,Trade_Record!P4,Commission_Listing!P4,Payment!P4,Template!P4,Transfer_Fee_Setting!P4,Security!P4,End_To_End!P4)</f>
         <v/>
       </c>
       <c r="L10">
-        <f>SUM(Login!Q4,Register!Q4,Deposit!Q4,Withdraw!Q4,Transfer!Q4,Convert!Q4,Global_Transfer!Q4,Profile!Q4,Wallets!Q4,End_To_End!Q4)</f>
+        <f>SUM(Login!Q4,Register!Q4,Deposit!Q4,Withdraw!Q4,Transfer!Q4,Convert!Q4,Global_Transfer!Q4,Profile!Q4,Wallets!Q4,Home!Q4,Bills!Q4,Trade_Record!Q4,Commission_Listing!Q4,Payment!Q4,Template!Q4,Transfer_Fee_Setting!Q4,Security!Q4,End_To_End!Q4)</f>
         <v/>
       </c>
       <c r="M10">
-        <f>SUM(Login!R4,Register!R4,Deposit!R4,Withdraw!R4,Transfer!R4,Convert!R4,Global_Transfer!R4,Profile!R4,Wallets!R4,End_To_End!R4)</f>
+        <f>SUM(Login!R4,Register!R4,Deposit!R4,Withdraw!R4,Transfer!R4,Convert!R4,Global_Transfer!R4,Profile!R4,Wallets!R4,Home!R4,Bills!R4,Trade_Record!R4,Commission_Listing!R4,Payment!R4,Template!R4,Transfer_Fee_Setting!R4,Security!R4,End_To_End!R4)</f>
         <v/>
       </c>
     </row>
@@ -1755,15 +5646,15 @@
         </is>
       </c>
       <c r="K11">
-        <f>SUM(Login!P5,Register!P5,Deposit!P5,Withdraw!P5,Transfer!P5,Convert!P5,Global_Transfer!P5,Profile!P5,Wallets!P5,End_To_End!P5)</f>
+        <f>SUM(Login!P5,Register!P5,Deposit!P5,Withdraw!P5,Transfer!P5,Convert!P5,Global_Transfer!P5,Profile!P5,Wallets!P5,Home!P5,Bills!P5,Trade_Record!P5,Commission_Listing!P5,Payment!P5,Template!P5,Transfer_Fee_Setting!P5,Security!P5,End_To_End!P5)</f>
         <v/>
       </c>
       <c r="L11">
-        <f>SUM(Login!Q5,Register!Q5,Deposit!Q5,Withdraw!Q5,Transfer!Q5,Convert!Q5,Global_Transfer!Q5,Profile!Q5,Wallets!Q5,End_To_End!Q5)</f>
+        <f>SUM(Login!Q5,Register!Q5,Deposit!Q5,Withdraw!Q5,Transfer!Q5,Convert!Q5,Global_Transfer!Q5,Profile!Q5,Wallets!Q5,Home!Q5,Bills!Q5,Trade_Record!Q5,Commission_Listing!Q5,Payment!Q5,Template!Q5,Transfer_Fee_Setting!Q5,Security!Q5,End_To_End!Q5)</f>
         <v/>
       </c>
       <c r="M11">
-        <f>SUM(Login!R5,Register!R5,Deposit!R5,Withdraw!R5,Transfer!R5,Convert!R5,Global_Transfer!R5,Profile!R5,Wallets!R5,End_To_End!R5)</f>
+        <f>SUM(Login!R5,Register!R5,Deposit!R5,Withdraw!R5,Transfer!R5,Convert!R5,Global_Transfer!R5,Profile!R5,Wallets!R5,Home!R5,Bills!R5,Trade_Record!R5,Commission_Listing!R5,Payment!R5,Template!R5,Transfer_Fee_Setting!R5,Security!R5,End_To_End!R5)</f>
         <v/>
       </c>
     </row>
@@ -1919,7 +5810,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>End_To_End</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1939,7 +5830,7 @@
         </is>
       </c>
       <c r="F23" s="9">
-        <f>COUNTIF(End_To_End!K:K,"PASS")</f>
+        <f>COUNTIF(Home!K:K,"PASS")</f>
         <v/>
       </c>
     </row>
@@ -1959,7 +5850,7 @@
         </is>
       </c>
       <c r="F24" s="9">
-        <f>COUNTIF(End_To_End!K:K,"FAIL")</f>
+        <f>COUNTIF(Home!K:K,"FAIL")</f>
         <v/>
       </c>
     </row>
@@ -1979,176 +5870,296 @@
         </is>
       </c>
       <c r="F25" s="9">
+        <f>COUNTIF(Home!K:K,"PENDING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Trade_Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C28" s="9">
+        <f>COUNTIF(Bills!K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F28" s="9">
+        <f>COUNTIF(Trade_Record!K:K,"PASS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C29" s="9">
+        <f>COUNTIF(Bills!K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F29" s="9">
+        <f>COUNTIF(Trade_Record!K:K,"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C30" s="9">
+        <f>COUNTIF(Bills!K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F30" s="9">
+        <f>COUNTIF(Trade_Record!K:K,"PENDING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Commission_Listing</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C33" s="9">
+        <f>COUNTIF(Commission_Listing!K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F33" s="9">
+        <f>COUNTIF(Payment!K:K,"PASS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C34" s="9">
+        <f>COUNTIF(Commission_Listing!K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F34" s="9">
+        <f>COUNTIF(Payment!K:K,"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C35" s="9">
+        <f>COUNTIF(Commission_Listing!K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F35" s="9">
+        <f>COUNTIF(Payment!K:K,"PENDING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Transfer_Fee_Setting</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C38" s="9">
+        <f>COUNTIF(Template!K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F38" s="9">
+        <f>COUNTIF(Transfer_Fee_Setting!K:K,"PASS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C39" s="9">
+        <f>COUNTIF(Template!K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F39" s="9">
+        <f>COUNTIF(Transfer_Fee_Setting!K:K,"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C40" s="9">
+        <f>COUNTIF(Template!K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F40" s="9">
+        <f>COUNTIF(Transfer_Fee_Setting!K:K,"PENDING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>End_To_End</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C43" s="9">
+        <f>COUNTIF(Security!K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F43" s="9">
+        <f>COUNTIF(End_To_End!K:K,"PASS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C44" s="9">
+        <f>COUNTIF(Security!K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F44" s="9">
+        <f>COUNTIF(End_To_End!K:K,"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C45" s="9">
+        <f>COUNTIF(Security!K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F45" s="9">
         <f>COUNTIF(End_To_End!K:K,"PENDING")</f>
         <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="C1" s="11" t="inlineStr">
-        <is>
-          <t>QA RESOURCES</t>
-        </is>
-      </c>
-      <c r="D1" s="11" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="E1" s="11" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="F1" s="11" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="G1" s="11" t="inlineStr">
-        <is>
-          <t>Test Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>DARA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>UMPay Android app</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Redmi 13C (Android)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>UMPAY</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>KIMA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>UMPay iOS app</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Android Emulator</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>WPAY</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VATHANA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>iPhone</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>OFL</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>UNCS</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -2298,7 +6309,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -2329,7 +6340,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="8">
@@ -2501,7 +6512,7 @@
         </is>
       </c>
       <c r="N9" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -2536,6 +6547,174 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
   </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>QA RESOURCES</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>Test Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DARA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>UMPay Android app</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Redmi 13C (Android)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>UMPAY</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>UMPay iOS app</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Android Emulator</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>WPAY</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VATHANA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>iPhone</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>UNCS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2682,7 +6861,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -2713,7 +6892,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="8">
@@ -2888,7 +7067,7 @@
         </is>
       </c>
       <c r="N9" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -3069,7 +7248,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -3100,7 +7279,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="8">
@@ -3253,7 +7432,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED, not failed - the device lost its network mid-run and the app answered "Network Error - Please check your internet connection", so signing in never completed and the scenario could not begin. Nothing here is a verdict on the application</t>
+          <t>BLOCKED, not failed - the Appium server exited part way through the run and no session could be opened, so the app was never asked anything. Nothing here is a verdict on the application</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -3272,7 +7451,7 @@
         </is>
       </c>
       <c r="N9" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -3453,7 +7632,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -3484,7 +7663,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="8">
@@ -3658,7 +7837,7 @@
         </is>
       </c>
       <c r="N9" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -3748,7 +7927,7 @@
         </is>
       </c>
       <c r="N10" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
@@ -3839,7 +8018,7 @@
         </is>
       </c>
       <c r="N11" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -3917,12 +8096,12 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+          <t>BLOCKED, not failed - the driver answered with an unknown server-side error, so the scenario never reached the point of asking the application anything: org.openqa.selenium.WebDriverException: An unknown server-side error occurred while processing the command. Original error: Could not proxy command to</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -3936,7 +8115,7 @@
         </is>
       </c>
       <c r="N12" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
@@ -4009,12 +8188,12 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+          <t>BLOCKED, not failed - the driver answered with an unknown server-side error, so the scenario never reached the point of asking the application anything: org.openqa.selenium.WebDriverException: An unknown server-side error occurred while processing the command. Original error: Could not proxy command to</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -4028,7 +8207,7 @@
         </is>
       </c>
       <c r="N13" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
@@ -4104,12 +8283,12 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+          <t>BLOCKED, not failed - the driver answered with an unknown server-side error, so the scenario never reached the point of asking the application anything: org.openqa.selenium.WebDriverException: An unknown server-side error occurred while processing the command. Original error: Could not proxy command to</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -4123,7 +8302,7 @@
         </is>
       </c>
       <c r="N14" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
@@ -4197,12 +8376,12 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
+          <t>BLOCKED, not failed - the driver answered with an unknown server-side error, so the scenario never reached the point of asking the application anything: org.openqa.selenium.WebDriverException:</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -4216,7 +8395,7 @@
         </is>
       </c>
       <c r="N15" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
@@ -4403,7 +8582,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -4434,7 +8613,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="8">
@@ -4587,12 +8766,12 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED, not failed - the device lost its network mid-run and the app answered "Network Error - Please check your internet connection", so signing in never completed and the scenario could not begin. Nothing here is a verdict on the application</t>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -4606,7 +8785,7 @@
         </is>
       </c>
       <c r="N9" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -4787,7 +8966,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -4818,7 +8997,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="8">
@@ -4976,12 +9155,12 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED, not failed - the driver answered with an unknown server-side error, so the scenario never reached the point of asking the application anything: org.openqa.selenium.WebDriverException: An unknown server-side error occurred while processing the command. Original error: Could not proxy command to</t>
+          <t>Ran on Redmi 13C (Android) and behaved as the scenario expects</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -4995,7 +9174,7 @@
         </is>
       </c>
       <c r="N9" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -5075,7 +9254,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>java.lang.AssertionError: The Transfer action never became enabled on a priced form expected [true] but found [false]</t>
+          <t>java.lang.AssertionError: The Transfer action never became enabled on a priced form expected [true] but found [false]. This was seen once and could not be re-confirmed: the device lost its UiAutomator2 server on both retries, so those runs are not evidence either way</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -5094,7 +9273,7 @@
         </is>
       </c>
       <c r="N10" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
@@ -5187,7 +9366,7 @@
         </is>
       </c>
       <c r="N11" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -5283,7 +9462,7 @@
         </is>
       </c>
       <c r="N12" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
@@ -5467,7 +9646,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -5498,7 +9677,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="8">
@@ -5667,7 +9846,7 @@
         </is>
       </c>
       <c r="N9" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -5756,7 +9935,7 @@
         </is>
       </c>
       <c r="N10" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
@@ -5848,7 +10027,7 @@
         </is>
       </c>
       <c r="N11" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -6031,7 +10210,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -6062,7 +10241,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="8">
@@ -6233,7 +10412,7 @@
         </is>
       </c>
       <c r="N9" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -6324,7 +10503,7 @@
         </is>
       </c>
       <c r="N10" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
@@ -6415,7 +10594,7 @@
         </is>
       </c>
       <c r="N11" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -6506,7 +10685,7 @@
         </is>
       </c>
       <c r="N12" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
@@ -6597,7 +10776,7 @@
         </is>
       </c>
       <c r="N13" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
@@ -6688,7 +10867,7 @@
         </is>
       </c>
       <c r="N14" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
@@ -6779,7 +10958,7 @@
         </is>
       </c>
       <c r="N15" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
@@ -6870,7 +11049,7 @@
         </is>
       </c>
       <c r="N16" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
@@ -6961,7 +11140,7 @@
         </is>
       </c>
       <c r="N17" s="13" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
